--- a/json/banco_de_dados.xlsx
+++ b/json/banco_de_dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bgccs-my.sharepoint.com/personal/pedro_ribeiro_bgcg_com/Documents/Documents/my docs/meus itens/programas/html/livros_espro/json/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bgccs-my.sharepoint.com/personal/pedro_ribeiro_bgcg_com/Documents/Documents/GitHub/site_espro/json/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="11_AD4D361C20488DEA4E38A035FC9A52745ADEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B750C4F-9C6A-41E9-BE04-0A206C49B5DF}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="11_AD4D361C20488DEA4E38A035FC9A52745ADEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F6ED75A-A8A5-40C0-9E80-065E268940AA}"/>
   <bookViews>
-    <workbookView xWindow="4185" yWindow="2775" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4185" yWindow="2775" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emprestimos" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
   <si>
     <t>Usuário</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>https://tse1.mm.bing.net/th/id/OIP.NPU-MZn_Geiny5BkbyBkqwHaHa?r=0&amp;rs=1&amp;pid=ImgDetMain&amp;o=7&amp;rm=3</t>
+  </si>
+  <si>
+    <t>telefone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo </t>
   </si>
 </sst>
 </file>
@@ -476,7 +482,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,9 +536,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,9 +561,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1021,7 +1021,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1269,7 +1269,12 @@
       <c r="C1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="9"/>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,10 +1395,10 @@
       <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1413,13 +1418,13 @@
       <c r="E2" s="6">
         <v>5</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="19">
         <v>3</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>1</v>
       </c>
     </row>
@@ -1439,13 +1444,13 @@
       <c r="E3" s="7">
         <v>4</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <v>2</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <v>2</v>
       </c>
     </row>
@@ -1465,13 +1470,13 @@
       <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <v>2</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <v>3</v>
       </c>
     </row>
@@ -1491,13 +1496,13 @@
       <c r="E5" s="7">
         <v>8</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="20">
         <v>6</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <v>4</v>
       </c>
     </row>
@@ -1517,13 +1522,13 @@
       <c r="E6" s="7">
         <v>6</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>5</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <v>5</v>
       </c>
     </row>
@@ -1543,13 +1548,13 @@
       <c r="E7" s="8">
         <v>4</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>3</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <v>6</v>
       </c>
     </row>
